--- a/www/download/IND.value.m.mv.WIOD16.xlsx
+++ b/www/download/IND.value.m.mv.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>1776588.68932884</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>1801181.97634754</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>1741946.89384447</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1367482.96478182</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>1224409.26846118</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>1141790.13861145</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1124766.89125316</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>998935.126452414</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>963222.628447848</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>1038497.43580508</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>854822.25781429</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>833652.976929521</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>805004.508448466</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>829774.134804774</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.868</t>
+          <t>867612.941411833</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1799107.78826731</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1745284.22269155</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>1522771.62915124</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1315818.18019781</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>1138449.93720299</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1042753.41853563</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>988016.041756673</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>843939.785043796</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>750928.26387148</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>852079.78468066</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>890618.042028106</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>841168.423122877</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>871901.106731533</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>883425.23272533</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>832213.081983215</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1307752.05353526</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1290636.91982053</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.206</t>
+          <t>1205177.83855885</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>1070807.53307289</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1001703.61748313</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>941474.695017366</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>912190.715135626</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>821191.551299462</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>764185.331794201</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>851982.071442752</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>913569.192121715</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>903314.314640421</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>891330.793299804</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866326.251314747</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.915</t>
+          <t>915077.999849041</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.436</t>
+          <t>11436431.6943599</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10179523.6007802</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.712</t>
+          <t>8711621.90132963</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6.797</t>
+          <t>6796655.04053598</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.484</t>
+          <t>5483775.35999314</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.732</t>
+          <t>4732075.36690272</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>4291665.93409836</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3.482</t>
+          <t>3482164.50308303</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3.018</t>
+          <t>3018347.1916232</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.192</t>
+          <t>3192130.87094423</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3.029</t>
+          <t>3028780.0531873</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2.607</t>
+          <t>2606840.32733877</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2689574.20812425</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.672</t>
+          <t>2672226.74753105</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>2705699.87720303</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.382</t>
+          <t>7381617.02859269</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8.266</t>
+          <t>8265479.4383483</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.787</t>
+          <t>8786000.30255235</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7.949</t>
+          <t>7948915.35816082</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7039638.11222065</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>5813694.36105664</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.836</t>
+          <t>4835543.26351598</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>3832462.27201382</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>3198912.48842862</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>3368823.71911164</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>2548861.12131079</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>2167956.68997553</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.268</t>
+          <t>2267964.0392394</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>2295495.94548471</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>2373891.77818658</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1304864.32894992</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>1323815.94145868</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1308875.33837801</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.212</t>
+          <t>1212032.48757061</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>1101383.36442165</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>980498.939644485</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>893347.700789074</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>783964.005111376</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>734031.566945686</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>795174.242424099</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>718628.424394514</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>695482.872485014</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>681786.812118978</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>663491.85145413</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>690327.202927803</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.021</t>
+          <t>23019642.1687554</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20.843</t>
+          <t>20840095.469653</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19.461</t>
+          <t>19458447.6916964</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17.711</t>
+          <t>17710069.596955</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>15319463.8549445</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>13.357</t>
+          <t>13355991.5426349</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.894</t>
+          <t>11893524.4210369</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9.477</t>
+          <t>9476251.54122486</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7.913</t>
+          <t>7912464.81795703</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7.602</t>
+          <t>7601135.83725244</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6.413</t>
+          <t>6412307.19458914</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5.641</t>
+          <t>5639907.10030699</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5.123</t>
+          <t>5122193.19188271</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4.546</t>
+          <t>4546168.53836047</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4.153</t>
+          <t>4153601.58186137</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2839759.66824721</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>2894781.24502909</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>2794343.21700838</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>2566533.12100351</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2.253</t>
+          <t>2252591.79193485</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>2047957.78090176</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>1854690.41491406</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1584896.37286489</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1.636</t>
+          <t>1636203.40677653</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>2327861.50006669</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1319854.73288133</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1252787.04739482</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1386181.22638569</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1482947.64284817</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1566266.60629788</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>4232368.94325059</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.751</t>
+          <t>3750562.84548617</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.241</t>
+          <t>3240378.670751</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>2637452.17576088</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2199431.64061781</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>1978015.85032299</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>1723398.47116678</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1451130.71113709</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1204728.44655707</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1390003.40656484</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1378188.03314616</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1290455.71535258</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1344496.4196276</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1380942.84508523</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1368956.17943609</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1466153.23997269</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1431311.57038091</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1348355.74874192</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1235914.77918072</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.105</t>
+          <t>1106963.30033549</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1091242.33324035</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1010235.46804736</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>869181.603405876</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>794970.821416886</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>872110.831828715</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>852285.329735562</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>780315.350135037</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>784360.124897566</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>768014.592082179</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>743445.789712012</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1338641.23791</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1321528.12698242</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1244183.47935909</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1137544.45099415</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1079306.23621455</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1011257.45346244</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>898084.715174551</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>787839.506653782</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>732223.721738077</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>772576.989638607</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>743373.554084735</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>694309.626342624</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>691980.064723317</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>685648.066634516</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>678808.318828958</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1785025.0642003</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.708</t>
+          <t>1707828.19818785</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1560070.23315864</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>1275369.29143952</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1125084.06731149</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>1052216.87630838</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1006255.39139532</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>854484.911642472</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>797133.766078307</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>851111.596981077</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>953088.780305404</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>933997.717289911</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>976046.647885357</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>936460.747349605</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>954299.072231082</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5.606</t>
+          <t>5605353.4787387</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.271</t>
+          <t>5269152.23603079</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4.579</t>
+          <t>4577558.28238242</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.824</t>
+          <t>3822349.98217834</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>3147476.36950908</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2629887.224831</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>2450738.72813676</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1.891</t>
+          <t>1891058.47630197</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.728</t>
+          <t>1727188.67700578</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1805799.31370486</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1.626</t>
+          <t>1625868.56957467</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1571675.16837625</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1574867.82294239</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1440148.32530024</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1405032.04627823</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1428810.57725751</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1411657.37137976</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1345537.97623085</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1202063.80674106</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>1066308.62726811</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1050516.24753936</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>993366.517719069</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>844138.026429604</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>815755.457435788</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>764989.311424003</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>775159.589616688</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>692216.931731536</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>741700.165698943</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>720909.138011505</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>672571.362630279</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>1251373.82094646</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1210895.65716418</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1139790.51769755</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.037</t>
+          <t>1036976.98477028</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>969188.060858393</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>933746.839686177</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.874</t>
+          <t>873527.569280088</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760017.001384752</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>698761.197989409</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>786975.768092872</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>753282.860158587</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>736631.136962455</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>744763.736836862</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>692850.416194851</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>691057.831531839</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1223354.91229166</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1253498.91803466</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>1258633.8521682</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1148279.3760725</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>952699.282337154</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>990928.919220913</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>904430.947117449</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754440.546932927</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>746132.086140464</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>904114.646106067</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>847345.091419444</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>844211.804424352</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>833058.255059952</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>844587.812234008</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>727017.338157437</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.656</t>
+          <t>2656516.84612405</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2820087.77441248</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.419</t>
+          <t>2418772.74087022</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.864</t>
+          <t>1863361.41207618</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>1581500.42107634</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>1631855.54164856</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1439213.22032309</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>1277977.63359253</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1020233.96946193</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1139902.9051708</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1139804.7473169</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1118802.87461554</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1173536.34011791</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1183681.87190319</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1204449.57841463</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5769482.96057996</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.023</t>
+          <t>5021775.19751621</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>4253831.06007248</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.488</t>
+          <t>3487459.65197834</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2.783</t>
+          <t>2782567.28812688</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.586</t>
+          <t>2585629.87874834</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.494</t>
+          <t>2493205.73525021</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.063</t>
+          <t>2062302.02502355</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.739</t>
+          <t>1739123.81498932</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.099</t>
+          <t>2099124.41550614</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>1881580.84591644</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>1708086.85648455</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.787</t>
+          <t>1786809.0133575</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.681</t>
+          <t>1681009.33390959</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1730279.59907127</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>18.817</t>
+          <t>18816168.5775337</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19.713</t>
+          <t>19711772.4355582</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>17.399</t>
+          <t>17398399.0379062</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15.798</t>
+          <t>15797183.1800073</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>14.892</t>
+          <t>14891367.0562952</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>12.819</t>
+          <t>12818390.721359</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>9.779</t>
+          <t>9778843.10530713</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>8359588.65706695</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>7.163</t>
+          <t>7162635.20883658</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>6.995</t>
+          <t>6994718.69921105</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>5.711</t>
+          <t>5710356.10350451</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>4.964</t>
+          <t>4963672.07753986</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>5.241</t>
+          <t>5240540.31658692</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>5.699</t>
+          <t>5698698.41713506</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>6.388</t>
+          <t>6388236.70959166</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>43.171</t>
+          <t>43169088.0434664</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>43.216</t>
+          <t>43209931.8519487</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>43.622</t>
+          <t>43618536.5337243</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>38.979</t>
+          <t>38978030.6786956</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>35.698</t>
+          <t>35697333.2093214</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>30.736</t>
+          <t>30734872.4069981</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>26.775</t>
+          <t>26774032.2769375</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>21.153</t>
+          <t>21150395.3874906</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19199157.7982915</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>18.999</t>
+          <t>18998347.0161152</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>15258312.9157965</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13.725</t>
+          <t>13723906.5024777</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15.953</t>
+          <t>15951877.9177123</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>17.152</t>
+          <t>17151439.435947</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>17.88</t>
+          <t>17880016.5416246</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>1398783.1569039</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1459108.18184381</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1332921.51138155</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>1087084.06645264</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>938466.141437498</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>960663.379616412</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>898098.616063826</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>763984.921538258</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>688969.252669077</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>908056.730631853</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>848164.868327679</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>812914.465967977</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>915597.003725591</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>887492.165297586</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>864183.62370191</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1457871.23080915</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1454223.81670625</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1333932.97036807</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1137485.99690224</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1034661.2134214</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>988667.445825158</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>970334.501023298</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>834813.335423087</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>770150.168884351</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>850564.101463614</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>891038.455798176</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870739.013450497</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>882010.22008138</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>834353.046764042</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>841217.434253496</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1595717.90619162</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.741</t>
+          <t>1738156.69288917</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>1777647.10431599</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>1731993.95687018</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1618906.89898116</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.575</t>
+          <t>1572925.7829968</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1602623.97655525</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1466258.40044456</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1294158.311243</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>1284818.8917754</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1169829.01870534</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1173210.48618001</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>1151415.89691714</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1317550.81636993</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>1390369.57345413</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.243</t>
+          <t>3243115.05881114</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>3404680.89799042</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3.213</t>
+          <t>3210924.28939074</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>3024577.73817291</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.792</t>
+          <t>2791420.76534908</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>2300292.45980173</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>2138980.43608209</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.838</t>
+          <t>1837603.36864751</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.938</t>
+          <t>1938089.75541336</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2.115</t>
+          <t>2114406.6735292</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.765</t>
+          <t>1764754.53959168</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>1746561.02156331</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>1718504.90319816</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>1715154.06459908</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1.613</t>
+          <t>1612706.19439669</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7.732</t>
+          <t>7732797.50415802</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6739412.33944399</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5.609</t>
+          <t>5607644.83818019</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4.535</t>
+          <t>4537179.49742354</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3.838</t>
+          <t>3838302.49242646</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3.386</t>
+          <t>3385201.56616578</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2.955</t>
+          <t>2953409.90424</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>2223654.51297234</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.881</t>
+          <t>1880774.50085756</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>2145487.86097653</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1874387.36993808</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1.607</t>
+          <t>1606804.17708701</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.709</t>
+          <t>1710088.55672615</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>1563872.85622403</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1615484.91948672</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>1062785.49401904</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1103304.15895378</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>965594.998620667</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>871058.667378378</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>782492.460199463</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>760321.320543764</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>715573.764081565</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>610662.061101575</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>739745.253401756</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>908369.654785457</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>928467.624564641</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>775634.540365703</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>903254.667765955</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754168.323886951</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>743630.31846366</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7.172</t>
+          <t>7171577.02716309</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>6758568.34538564</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6.087</t>
+          <t>6086347.53404624</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4.947</t>
+          <t>4947031.80325617</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3.946</t>
+          <t>3945691.42762944</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3.547</t>
+          <t>3546649.1663232</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>3091822.725274</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>2255008.51141603</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>2020729.18388638</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2.173</t>
+          <t>2172452.53381104</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2.015</t>
+          <t>2014959.20505783</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>1864183.6046303</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>1977621.28134102</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1.807</t>
+          <t>1807296.01698897</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1806465.31885274</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.188</t>
+          <t>3187723.92813294</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.007</t>
+          <t>3006295.41128399</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.985</t>
+          <t>2984051.21957392</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>3114807.4074291</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>3005135.05639507</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2709649.05686266</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.563</t>
+          <t>2562359.20119026</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.399</t>
+          <t>2398643.45245506</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.282</t>
+          <t>2281240.9686968</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>2704766.43215316</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>2397729.94361657</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2.231</t>
+          <t>2230230.67337191</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2.238</t>
+          <t>2237776.59349869</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>2116791.87079778</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2.132</t>
+          <t>2132531.77937081</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2.517</t>
+          <t>2517090.48979362</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2469195.20477459</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>2211245.90649712</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2.315</t>
+          <t>2315321.94178092</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>1734024.42520912</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1692156.13387473</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1615243.26390987</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>1472188.15771435</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1560080.72294286</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1465227.60659784</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1471874.95143449</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1367022.67123768</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1713414.61460579</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1395955.14346766</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1309247.02009047</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1350672.96061874</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1362009.58231543</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1352678.51464639</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.276</t>
+          <t>1275807.45619909</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1104379.45833477</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1021659.61501624</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.977</t>
+          <t>977224.296941785</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>855019.765962058</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>817998.801383675</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>1094290.69819987</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>1181270.58795882</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1109474.15000841</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>1091869.80182562</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1.242</t>
+          <t>1241632.97043629</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1.214</t>
+          <t>1214819.62647668</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.633</t>
+          <t>4632969.16796955</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.247</t>
+          <t>4246674.33439814</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3959217.22652646</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.589</t>
+          <t>3588501.05954333</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.063</t>
+          <t>3062952.66255812</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>2718077.66327716</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>2469270.01725645</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>2041780.1030178</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.756</t>
+          <t>1755683.97530802</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.161</t>
+          <t>2161114.40976916</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.983</t>
+          <t>1982839.96176725</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1759859.74799099</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>1858271.40972179</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>1804872.27321612</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.764</t>
+          <t>1764110.30085138</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>2961762.49392489</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.923</t>
+          <t>2923037.010267</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2.656</t>
+          <t>2656065.52678169</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.233</t>
+          <t>2233182.50032712</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2.061</t>
+          <t>2061170.60741059</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.893</t>
+          <t>1892519.24496397</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>1822074.67738006</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1578040.57391985</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1442687.89234458</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>1.482</t>
+          <t>1481875.34866723</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1431826.30639669</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1404818.52628559</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>1458097.25774086</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1405573.67726997</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1.428</t>
+          <t>1428142.06267081</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15.088</t>
+          <t>15088161.6714897</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>13279575.3748007</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11.154</t>
+          <t>11153463.481263</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8.682</t>
+          <t>8681625.85546787</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6.595</t>
+          <t>6594582.57072223</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>5.387</t>
+          <t>5386559.70722659</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4.283</t>
+          <t>4283178.68184254</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>3.336</t>
+          <t>3335201.83895563</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2.678</t>
+          <t>2678033.0415828</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2.964</t>
+          <t>2963741.243761</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2.664</t>
+          <t>2663465.92729351</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2.436</t>
+          <t>2435711.92378612</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2.319</t>
+          <t>2318542.46255531</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>2048262.9367316</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2060462.94382599</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11.586</t>
+          <t>11586261.8324074</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9.544</t>
+          <t>9542572.53803021</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8.485</t>
+          <t>8483813.71645606</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>7.283</t>
+          <t>7283086.87948664</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5.278</t>
+          <t>5277359.68613592</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4.406</t>
+          <t>4405681.31591996</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>3464696.79876643</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.617</t>
+          <t>2617082.17028452</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1931969.14868893</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>2450799.08647256</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>2121393.22063344</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>1723160.11208849</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1.721</t>
+          <t>1721114.91366652</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.581</t>
+          <t>1581132.18358462</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.606</t>
+          <t>1605764.4627739</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5.571</t>
+          <t>5570643.53038642</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5.227</t>
+          <t>5218712.85694044</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4.409</t>
+          <t>4408681.80277529</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3.231</t>
+          <t>3234688.97135604</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>2701492.82334872</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>2486296.29387626</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>2215149.81400623</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.717</t>
+          <t>1717521.82382103</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.396</t>
+          <t>1395760.6139131</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.634</t>
+          <t>1633748.62791045</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1529117.8385233</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1438744.3973831</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1471149.10188441</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1413317.72991126</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1361713.20277476</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>2712408.0153975</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2.695</t>
+          <t>2695210.80273661</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.485</t>
+          <t>2484613.22591174</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2090096.32664618</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1909403.16102555</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.766</t>
+          <t>1766651.43282022</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1641196.86803293</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>1348484.88158308</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1210754.26412784</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1339771.44639255</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1327306.37607147</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1273765.66285294</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1.341</t>
+          <t>1340264.72942602</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1259644.23061138</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1212712.48246172</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.233</t>
+          <t>1233071.51180312</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1239139.29285904</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1140962.59535576</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>973154.200525532</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>898301.139506653</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>885161.275882862</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810995.322945626</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>686893.538541132</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>648642.031939721</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>752587.843886082</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>680047.192755413</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>633429.583785244</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>638904.772621042</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>630259.655273116</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634115.721963156</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.683</t>
+          <t>4682515.13915769</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6.246</t>
+          <t>6244400.76705248</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5318476.61125763</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>4111347.04498016</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>3.487</t>
+          <t>3486589.46088637</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>2908600.79415135</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2.684</t>
+          <t>2683388.85819353</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2.193</t>
+          <t>2191898.01737723</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.967</t>
+          <t>1966712.13490898</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2.277</t>
+          <t>2276360.45431829</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>2043331.58838113</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>2040935.92459505</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2.113</t>
+          <t>2112456.40856134</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2.198</t>
+          <t>2197740.1830699</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2.446</t>
+          <t>2446338.15842017</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5.157</t>
+          <t>5155882.8463279</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5.338</t>
+          <t>5335952.38110324</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5.377</t>
+          <t>5375564.85040562</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>5.392</t>
+          <t>5391404.53996637</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5.039</t>
+          <t>5037894.85319807</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>4.604</t>
+          <t>4603267.72486386</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>4.374</t>
+          <t>4373438.13385918</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>4.119</t>
+          <t>4117378.48942155</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3.911</t>
+          <t>3910374.60948971</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>3958729.6010544</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>3.567</t>
+          <t>3566080.1795508</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>3249714.56463333</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3278995.93710915</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>3198646.51228393</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>3.216</t>
+          <t>3216495.53364134</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1378774.93979272</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1315479.12722113</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1343184.88439505</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1274027.46025984</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.234</t>
+          <t>1233192.09437297</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>1169080.09354541</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>1102005.30618859</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>968292.138101368</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>919337.732874755</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>898141.755120958</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>841477.433037123</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>844085.06626625</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>801429.101616206</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>768181.510772473</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>751588.742532256</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>16.802</t>
+          <t>16802031.0305368</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17.253</t>
+          <t>17252196.9716406</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17.727</t>
+          <t>17726185.2683816</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17.017</t>
+          <t>17016659.5487355</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>15.561</t>
+          <t>15560011.8218863</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>13979255.2454916</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>12.459</t>
+          <t>12458708.1815472</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>10.449</t>
+          <t>10448633.5705591</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>9.195</t>
+          <t>9194510.77014501</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>9.727</t>
+          <t>9727075.27482761</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>8.471</t>
+          <t>8470723.22198249</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>7.785</t>
+          <t>7783863.78196208</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>7.818</t>
+          <t>7817716.18539073</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>7710382.54007952</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>7.759</t>
+          <t>7759152.4321359</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>250.12</t>
+          <t>250104856.804533</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>242.348</t>
+          <t>242303294.206304</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>226.143</t>
+          <t>226106643.630329</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>198.788</t>
+          <t>198775582.8274</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>174.253</t>
+          <t>174243357.692179</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>153.973</t>
+          <t>153963481.813936</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>135.843</t>
+          <t>135835914.806612</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>111.925</t>
+          <t>111902867.510114</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>99.572</t>
+          <t>99560830.5365557</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>105.742</t>
+          <t>105737020.108591</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>92.824</t>
+          <t>92811122.2087574</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>85.032</t>
+          <t>85011941.856457</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>88.678</t>
+          <t>88669911.4057298</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>88.083</t>
+          <t>88083004.1072635</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>89.322</t>
+          <t>89325181.6666303</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5169767.16321785</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4.432</t>
+          <t>4431854.763816</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3.919</t>
+          <t>3918441.70233614</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>3.149</t>
+          <t>3148520.47856787</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>2645901.36715045</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2.509</t>
+          <t>2509032.25912026</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>2204697.65453547</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.817</t>
+          <t>1816903.57747353</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>1631966.06097545</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1742399.81373109</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1830251.33563411</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1739641.40444603</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.843</t>
+          <t>1843310.4440662</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>1886065.53839724</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>1915885.26542336</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1578176.57265543</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.501</t>
+          <t>1500134.72929158</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1350658.71595913</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1190760.24493119</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1018642.27420553</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1023972.94155454</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1010236.31624508</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>882881.466368295</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>774089.361270454</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>780673.798580232</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>706858.021018808</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>679760.794754086</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>712652.788927873</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>692155.444431483</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>672598.986706159</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1226195.01055633</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>1122597.62734903</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>991092.189920898</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>905879.13256831</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>801741.964453975</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>726343.357544991</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>632129.962095466</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>547679.188859236</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492031.317821872</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>514099.858103397</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>467839.601815778</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>448284.047838479</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>435479.641079392</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>428255.070488273</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>416584.124673303</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
